--- a/Pruebas calificadas/SANTIAGO DE LAS ATALAYAS-301_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/SANTIAGO DE LAS ATALAYAS-301_Ajustado_CALIFICADO.xlsx
@@ -10883,7 +10883,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1141358601</t>
+          <t>1025560504</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1141358601</t>
+          <t>1025560504</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
